--- a/booking_forms/042_travel_agency_booking_form_template--booking_forms.xlsx
+++ b/booking_forms/042_travel_agency_booking_form_template--booking_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>guest_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Guest Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>travel_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Travel Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>accommodation_options</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Accommodation Options</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Special Requests</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>payment_information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Payment Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>security_insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Security and Insurance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>travel_agency_booking_form</t>
+          <t>review_and_confirm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travel Agency Booking Form</t>
+          <t>Review and Confirm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
